--- a/2. Extracting affilitations from Tesseract/2.2. Fuzzy Matching/2.2.A. Data created in 2.2. AER/AER 1970-1971 first pass affiliations.xlsx
+++ b/2. Extracting affilitations from Tesseract/2.2. Fuzzy Matching/2.2.A. Data created in 2.2. AER/AER 1970-1971 first pass affiliations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ137"/>
+  <dimension ref="A1:AR137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,155 +486,160 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Split method</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>0_Auth_string_found</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>0_Auth_affs_0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>0_Auth_affs_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>0_Auth_affs_2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>0_Auth_affs_3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>0_Auth_affs_4</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>1_Auth_string_found</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>1_Auth_affs_0</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>1_Auth_affs_1</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>1_Auth_affs_2</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>1_Auth_affs_3</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>1_Auth_affs_4</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>2_Auth_string_found</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>2_Auth_affs_0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>2_Auth_affs_1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>2_Auth_affs_2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>2_Auth_affs_3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>2_Auth_affs_4</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>3_Auth_string_found</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>3_Auth_affs_0</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>3_Auth_affs_1</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>3_Auth_affs_2</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>3_Auth_affs_3</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>3_Auth_affs_4</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>4_Auth_affs_0</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>4_Auth_affs_1</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>4_Auth_affs_2</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>4_Auth_affs_3</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>5_Auth_affs_0</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>6_Auth_affs_0</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>7_Auth_affs_0</t>
         </is>
@@ -731,17 +736,17 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Brookings Institution</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>University Of Maryland</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -769,6 +774,7 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -832,6 +838,7 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -895,6 +902,7 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -958,6 +966,7 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1021,6 +1030,7 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1084,6 +1094,7 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1147,6 +1158,7 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1210,6 +1222,7 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1273,6 +1286,7 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1336,6 +1350,7 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1399,6 +1414,7 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1462,6 +1478,7 @@
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1525,6 +1542,7 @@
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1588,6 +1606,7 @@
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1651,6 +1670,7 @@
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1714,6 +1734,7 @@
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1777,6 +1798,7 @@
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1840,6 +1862,7 @@
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1903,6 +1926,7 @@
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1966,6 +1990,7 @@
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2029,6 +2054,7 @@
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2092,6 +2118,7 @@
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2155,6 +2182,7 @@
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2218,6 +2246,7 @@
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2281,6 +2310,7 @@
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2344,6 +2374,7 @@
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2407,6 +2438,7 @@
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2470,6 +2502,7 @@
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2533,6 +2566,7 @@
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2596,6 +2630,7 @@
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2659,6 +2694,7 @@
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2722,6 +2758,7 @@
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2785,6 +2822,7 @@
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2848,6 +2886,7 @@
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2911,6 +2950,7 @@
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2987,12 +3027,12 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>University Of New Hampshire</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -3021,6 +3061,7 @@
       <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3103,12 +3144,12 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>UCSB</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -3137,6 +3178,7 @@
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
       <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3217,12 +3259,12 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -3251,6 +3293,7 @@
       <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3317,17 +3360,17 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>University Of Minnesota</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -3355,6 +3398,7 @@
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
       <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3439,17 +3483,17 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>Hebrew University</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Hebrew University Of Jerusalem</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -3477,6 +3521,7 @@
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
       <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3551,12 +3596,12 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>University Of Chicago</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -3585,6 +3630,7 @@
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3653,12 +3699,12 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>University Of Michigan</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3687,6 +3733,7 @@
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
       <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3779,12 +3826,12 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>Simon Fraser University</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -3813,6 +3860,7 @@
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3888,24 +3936,28 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t xml:space="preserve">* 'The Authors Are Assistant Professor Of Economics, Massachusetts Institute Of Technology </t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Massachusetts Institute Of Technology</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
         <is>
           <t xml:space="preserve"> Research Fellow, Institute For Development Studies, University College, Nairobi, </t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
@@ -3929,6 +3981,7 @@
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
       <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4001,12 +4054,12 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>Bell Telephone Laboratories, Inc.</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -4035,6 +4088,7 @@
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="inlineStr"/>
       <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4145,12 +4199,12 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -4179,6 +4233,7 @@
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="inlineStr"/>
       <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4249,12 +4304,12 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
         <is>
           <t>Brown University</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -4283,6 +4338,7 @@
       <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="inlineStr"/>
       <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4363,12 +4419,12 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
         <is>
           <t>University Of Pennsylvania</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -4397,6 +4453,7 @@
       <c r="AO49" t="inlineStr"/>
       <c r="AP49" t="inlineStr"/>
       <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4465,17 +4522,17 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>Rand Corporation</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -4503,6 +4560,7 @@
       <c r="AO50" t="inlineStr"/>
       <c r="AP50" t="inlineStr"/>
       <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4566,6 +4624,7 @@
       <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -4665,32 +4724,36 @@
 Massachusetts Institute Of Technology.</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Author Surname</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
         <is>
           <t>Brown University</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Massachusetts Institute Of Technology</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
         <is>
           <t>Brown University</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>Massachusetts Institute Of Technology</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -4712,6 +4775,7 @@
       <c r="AO52" t="inlineStr"/>
       <c r="AP52" t="inlineStr"/>
       <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4808,6 +4872,7 @@
       <c r="AO53" t="inlineStr"/>
       <c r="AP53" t="inlineStr"/>
       <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4871,6 +4936,7 @@
       <c r="AO54" t="inlineStr"/>
       <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4934,6 +5000,7 @@
       <c r="AO55" t="inlineStr"/>
       <c r="AP55" t="inlineStr"/>
       <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4997,6 +5064,7 @@
       <c r="AO56" t="inlineStr"/>
       <c r="AP56" t="inlineStr"/>
       <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5060,6 +5128,7 @@
       <c r="AO57" t="inlineStr"/>
       <c r="AP57" t="inlineStr"/>
       <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5123,6 +5192,7 @@
       <c r="AO58" t="inlineStr"/>
       <c r="AP58" t="inlineStr"/>
       <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5186,6 +5256,7 @@
       <c r="AO59" t="inlineStr"/>
       <c r="AP59" t="inlineStr"/>
       <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5249,6 +5320,7 @@
       <c r="AO60" t="inlineStr"/>
       <c r="AP60" t="inlineStr"/>
       <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5312,6 +5384,7 @@
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -5375,6 +5448,7 @@
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
       <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -5438,6 +5512,7 @@
       <c r="AO63" t="inlineStr"/>
       <c r="AP63" t="inlineStr"/>
       <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -5501,6 +5576,7 @@
       <c r="AO64" t="inlineStr"/>
       <c r="AP64" t="inlineStr"/>
       <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -5564,6 +5640,7 @@
       <c r="AO65" t="inlineStr"/>
       <c r="AP65" t="inlineStr"/>
       <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -5627,6 +5704,7 @@
       <c r="AO66" t="inlineStr"/>
       <c r="AP66" t="inlineStr"/>
       <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -5723,6 +5801,7 @@
       <c r="AO67" t="inlineStr"/>
       <c r="AP67" t="inlineStr"/>
       <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5786,6 +5865,7 @@
       <c r="AO68" t="inlineStr"/>
       <c r="AP68" t="inlineStr"/>
       <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5849,6 +5929,7 @@
       <c r="AO69" t="inlineStr"/>
       <c r="AP69" t="inlineStr"/>
       <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -5912,6 +5993,7 @@
       <c r="AO70" t="inlineStr"/>
       <c r="AP70" t="inlineStr"/>
       <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6001,34 +6083,38 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
           <t xml:space="preserve">* 'The Authors Are, Respectively, Associate Professor Of Industrial Management At Purdue University </t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Purdue University</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr">
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
         <is>
           <t xml:space="preserve"> Associate Professor Of Finance At The University Of Utah. 'The Research Was Supported With Funds Supplied By The National Bureau Of Economic Research, The Purdue Research Foundation, </t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>National Bureau Of Economic Research</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>University Of Utah</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -6050,6 +6136,7 @@
       <c r="AO71" t="inlineStr"/>
       <c r="AP71" t="inlineStr"/>
       <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -6129,29 +6216,33 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
           <t xml:space="preserve">* 'The Authors Are Assistant Professors Of Economics At Princeton University </t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr">
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
         <is>
           <t xml:space="preserve"> Yale University, </t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
@@ -6174,6 +6265,7 @@
       <c r="AO72" t="inlineStr"/>
       <c r="AP72" t="inlineStr"/>
       <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -6248,12 +6340,12 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
         <is>
           <t>University Of Minnesota</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -6282,6 +6374,7 @@
       <c r="AO73" t="inlineStr"/>
       <c r="AP73" t="inlineStr"/>
       <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -6356,12 +6449,12 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -6390,6 +6483,7 @@
       <c r="AO74" t="inlineStr"/>
       <c r="AP74" t="inlineStr"/>
       <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -6473,29 +6567,33 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
           <t xml:space="preserve">*' The Authors Are, Respectively, Visiting Associate Professor At The University Of Illinois </t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>University Of Illinois</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr">
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
         <is>
           <t xml:space="preserve"> Senior Lecturer At The Hebrew University, Jerusalem. They Wish To Acknowledge The Helpful Comments Of Moshe Ben-Horim, Gad Marx, </t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>Hebrew University</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -6518,6 +6616,7 @@
       <c r="AO75" t="inlineStr"/>
       <c r="AP75" t="inlineStr"/>
       <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -6600,27 +6699,27 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
         <is>
           <t>Brookings Institution</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>International Monetary Fund</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>University Of British Columbia</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>University Of Chicago</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
@@ -6646,6 +6745,7 @@
       <c r="AO76" t="inlineStr"/>
       <c r="AP76" t="inlineStr"/>
       <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -6730,12 +6830,12 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -6764,6 +6864,7 @@
       <c r="AO77" t="inlineStr"/>
       <c r="AP77" t="inlineStr"/>
       <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -6838,17 +6939,17 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
         <is>
           <t>University Of North Carolina</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>University Of North Carolina At Chapel Hill</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -6876,6 +6977,7 @@
       <c r="AO78" t="inlineStr"/>
       <c r="AP78" t="inlineStr"/>
       <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -6968,22 +7070,22 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
         <is>
           <t>Agency For International Development</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>Food Research Institute</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
@@ -7010,6 +7112,7 @@
       <c r="AO79" t="inlineStr"/>
       <c r="AP79" t="inlineStr"/>
       <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -7097,29 +7200,33 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t xml:space="preserve">* Princeton University </t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr">
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
         <is>
           <t xml:space="preserve"> University Of British Columbia, </t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>University Of British Columbia</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
@@ -7142,6 +7249,7 @@
       <c r="AO80" t="inlineStr"/>
       <c r="AP80" t="inlineStr"/>
       <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -7218,12 +7326,12 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
         <is>
           <t>Virginia Polytechnic Institute</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -7252,6 +7360,7 @@
       <c r="AO81" t="inlineStr"/>
       <c r="AP81" t="inlineStr"/>
       <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -7319,25 +7428,29 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
           <t xml:space="preserve">* The Authors Are, Respectively, Professor Of Agricultural Economics </t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr">
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
         <is>
           <t xml:space="preserve"> Economics At Montana State University, </t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>Montana State University</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
@@ -7360,6 +7473,7 @@
       <c r="AO82" t="inlineStr"/>
       <c r="AP82" t="inlineStr"/>
       <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -7427,35 +7541,39 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t xml:space="preserve">* 'The Authors Are Professor Of Economics </t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
         <is>
           <t xml:space="preserve"> Finance </t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>Finance Department</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>Frankfurt School Of Finance</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>Shanghai University Of Finance</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
@@ -7476,6 +7594,7 @@
       <c r="AO83" t="inlineStr"/>
       <c r="AP83" t="inlineStr"/>
       <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -7558,17 +7677,17 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
         <is>
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>Southern Methodist University</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
@@ -7596,6 +7715,7 @@
       <c r="AO84" t="inlineStr"/>
       <c r="AP84" t="inlineStr"/>
       <c r="AQ84" t="inlineStr"/>
+      <c r="AR84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -7674,12 +7794,12 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
         <is>
           <t>University Of Missouri</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -7708,6 +7828,7 @@
       <c r="AO85" t="inlineStr"/>
       <c r="AP85" t="inlineStr"/>
       <c r="AQ85" t="inlineStr"/>
+      <c r="AR85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -7780,12 +7901,12 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -7814,6 +7935,7 @@
       <c r="AO86" t="inlineStr"/>
       <c r="AP86" t="inlineStr"/>
       <c r="AQ86" t="inlineStr"/>
+      <c r="AR86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -7892,12 +8014,12 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
         <is>
           <t>Queen'S University</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -7926,6 +8048,7 @@
       <c r="AO87" t="inlineStr"/>
       <c r="AP87" t="inlineStr"/>
       <c r="AQ87" t="inlineStr"/>
+      <c r="AR87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -8011,6 +8134,7 @@
       <c r="AO88" t="inlineStr"/>
       <c r="AP88" t="inlineStr"/>
       <c r="AQ88" t="inlineStr"/>
+      <c r="AR88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -8099,12 +8223,12 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
         <is>
           <t>University Of Washington</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -8133,6 +8257,7 @@
       <c r="AO89" t="inlineStr"/>
       <c r="AP89" t="inlineStr"/>
       <c r="AQ89" t="inlineStr"/>
+      <c r="AR89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -8213,12 +8338,12 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
         <is>
           <t>University Of Michigan</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -8247,6 +8372,7 @@
       <c r="AO90" t="inlineStr"/>
       <c r="AP90" t="inlineStr"/>
       <c r="AQ90" t="inlineStr"/>
+      <c r="AR90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -8325,12 +8451,12 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
         <is>
           <t>Suny At Buffalo</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -8359,6 +8485,7 @@
       <c r="AO91" t="inlineStr"/>
       <c r="AP91" t="inlineStr"/>
       <c r="AQ91" t="inlineStr"/>
+      <c r="AR91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -8456,33 +8583,37 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
           <t xml:space="preserve">* Associate Professor, Department Of Economics, Tovko Metropolitan University Now Visiting Associate Professor, Department Of Agricultural Economics, University Of Minnesota, </t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>Tokyo Metropolitan University</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>University Of Minnesota</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr">
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
         <is>
           <t xml:space="preserve"> Professor, Department Of Agricultural Economics, University Of Minnesota, </t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>University Of Minnesota</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
@@ -8505,6 +8636,7 @@
       <c r="AO92" t="inlineStr"/>
       <c r="AP92" t="inlineStr"/>
       <c r="AQ92" t="inlineStr"/>
+      <c r="AR92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -8581,12 +8713,12 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
         <is>
           <t>Monash University</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -8615,6 +8747,7 @@
       <c r="AO93" t="inlineStr"/>
       <c r="AP93" t="inlineStr"/>
       <c r="AQ93" t="inlineStr"/>
+      <c r="AR93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -8691,17 +8824,17 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
         <is>
           <t>Florida State University</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr"/>
@@ -8729,6 +8862,7 @@
       <c r="AO94" t="inlineStr"/>
       <c r="AP94" t="inlineStr"/>
       <c r="AQ94" t="inlineStr"/>
+      <c r="AR94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -8791,12 +8925,12 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
         <is>
           <t>University Of Washington</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -8825,6 +8959,7 @@
       <c r="AO95" t="inlineStr"/>
       <c r="AP95" t="inlineStr"/>
       <c r="AQ95" t="inlineStr"/>
+      <c r="AR95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -8887,12 +9022,12 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -8921,6 +9056,7 @@
       <c r="AO96" t="inlineStr"/>
       <c r="AP96" t="inlineStr"/>
       <c r="AQ96" t="inlineStr"/>
+      <c r="AR96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -8995,12 +9131,12 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
         <is>
           <t>UCLA</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -9029,6 +9165,7 @@
       <c r="AO97" t="inlineStr"/>
       <c r="AP97" t="inlineStr"/>
       <c r="AQ97" t="inlineStr"/>
+      <c r="AR97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -9097,12 +9234,12 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
         <is>
           <t>University Of Michigan</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -9131,6 +9268,7 @@
       <c r="AO98" t="inlineStr"/>
       <c r="AP98" t="inlineStr"/>
       <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -9197,12 +9335,12 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
         <is>
           <t>Washington University</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -9231,6 +9369,7 @@
       <c r="AO99" t="inlineStr"/>
       <c r="AP99" t="inlineStr"/>
       <c r="AQ99" t="inlineStr"/>
+      <c r="AR99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -9286,32 +9425,36 @@
           <t>* "The Hebrew University Of Jerusalem.</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
         <is>
           <t>Hebrew University</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>Hebrew University Of Jerusalem</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr">
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr">
         <is>
           <t>Hebrew University</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>Hebrew University Of Jerusalem</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
@@ -9333,6 +9476,7 @@
       <c r="AO100" t="inlineStr"/>
       <c r="AP100" t="inlineStr"/>
       <c r="AQ100" t="inlineStr"/>
+      <c r="AR100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -9443,17 +9587,17 @@
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr">
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
         <is>
           <t>University Of British Columbia</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
@@ -9481,6 +9625,7 @@
       <c r="AO101" t="inlineStr"/>
       <c r="AP101" t="inlineStr"/>
       <c r="AQ101" t="inlineStr"/>
+      <c r="AR101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -9568,29 +9713,33 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
           <t xml:space="preserve">* Assistant Professors At The University Of Wisconsin </t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr">
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr">
         <is>
           <t xml:space="preserve"> Rice University, </t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>Rice University</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
@@ -9613,6 +9762,7 @@
       <c r="AO102" t="inlineStr"/>
       <c r="AP102" t="inlineStr"/>
       <c r="AQ102" t="inlineStr"/>
+      <c r="AR102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -9687,17 +9837,17 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
         <is>
           <t>National Bureau Of Economic Research</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
@@ -9725,6 +9875,7 @@
       <c r="AO103" t="inlineStr"/>
       <c r="AP103" t="inlineStr"/>
       <c r="AQ103" t="inlineStr"/>
+      <c r="AR103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -9799,17 +9950,17 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
         <is>
           <t>University Of Minnesota</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>University Of Notre Dame</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
@@ -9837,6 +9988,7 @@
       <c r="AO104" t="inlineStr"/>
       <c r="AP104" t="inlineStr"/>
       <c r="AQ104" t="inlineStr"/>
+      <c r="AR104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -9900,6 +10052,7 @@
       <c r="AO105" t="inlineStr"/>
       <c r="AP105" t="inlineStr"/>
       <c r="AQ105" t="inlineStr"/>
+      <c r="AR105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -9963,6 +10116,7 @@
       <c r="AO106" t="inlineStr"/>
       <c r="AP106" t="inlineStr"/>
       <c r="AQ106" t="inlineStr"/>
+      <c r="AR106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -10026,6 +10180,7 @@
       <c r="AO107" t="inlineStr"/>
       <c r="AP107" t="inlineStr"/>
       <c r="AQ107" t="inlineStr"/>
+      <c r="AR107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -10089,6 +10244,7 @@
       <c r="AO108" t="inlineStr"/>
       <c r="AP108" t="inlineStr"/>
       <c r="AQ108" t="inlineStr"/>
+      <c r="AR108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -10174,6 +10330,7 @@
       <c r="AO109" t="inlineStr"/>
       <c r="AP109" t="inlineStr"/>
       <c r="AQ109" t="inlineStr"/>
+      <c r="AR109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -10262,17 +10419,17 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
         <is>
           <t>University Of Minnesota</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>University Of Western Ontario</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
@@ -10300,6 +10457,7 @@
       <c r="AO110" t="inlineStr"/>
       <c r="AP110" t="inlineStr"/>
       <c r="AQ110" t="inlineStr"/>
+      <c r="AR110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -10381,46 +10539,50 @@
 Fn. 4 Below.</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr">
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>University Of Maryland</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr">
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="V111" t="inlineStr">
         <is>
           <t>University Of Maryland</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr">
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="AA111" t="inlineStr">
+      <c r="AB111" t="inlineStr">
         <is>
           <t>University Of Maryland</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr"/>
@@ -10436,6 +10598,7 @@
       <c r="AO111" t="inlineStr"/>
       <c r="AP111" t="inlineStr"/>
       <c r="AQ111" t="inlineStr"/>
+      <c r="AR111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -10568,17 +10731,17 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
         <is>
           <t>Bureau Of The Census</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="P112" t="inlineStr">
         <is>
           <t>University Of Chicago</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
@@ -10606,6 +10769,7 @@
       <c r="AO112" t="inlineStr"/>
       <c r="AP112" t="inlineStr"/>
       <c r="AQ112" t="inlineStr"/>
+      <c r="AR112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -10662,12 +10826,12 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
         <is>
           <t>Yale University</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
@@ -10696,6 +10860,7 @@
       <c r="AO113" t="inlineStr"/>
       <c r="AP113" t="inlineStr"/>
       <c r="AQ113" t="inlineStr"/>
+      <c r="AR113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -10768,17 +10933,17 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
         <is>
           <t>Federal Deposit Insurance Corporation</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>Indiana University</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr"/>
@@ -10806,6 +10971,7 @@
       <c r="AO114" t="inlineStr"/>
       <c r="AP114" t="inlineStr"/>
       <c r="AQ114" t="inlineStr"/>
+      <c r="AR114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -10885,29 +11051,33 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
           <t xml:space="preserve">*'The Authors, Assistant Professors Of Economics At Harvard University </t>
         </is>
       </c>
-      <c r="N115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr">
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr">
         <is>
           <t xml:space="preserve"> The University Of Pennsylvania, Respectively, Are Grateful To Richard Caves, Gottfried Haberler, Thomas Horst, Harry Johnson, Murray Kemp, Robert Mundell, Lawrence Officer, Trevor Underwood, </t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="U115" t="inlineStr">
         <is>
           <t>University Of Pennsylvania</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
@@ -10930,6 +11100,7 @@
       <c r="AO115" t="inlineStr"/>
       <c r="AP115" t="inlineStr"/>
       <c r="AQ115" t="inlineStr"/>
+      <c r="AR115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -10998,17 +11169,17 @@
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
         <is>
           <t>Fordham University</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
+      <c r="P116" t="inlineStr">
         <is>
           <t>New York University</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
@@ -11036,6 +11207,7 @@
       <c r="AO116" t="inlineStr"/>
       <c r="AP116" t="inlineStr"/>
       <c r="AQ116" t="inlineStr"/>
+      <c r="AR116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -11104,17 +11276,17 @@
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
         <is>
           <t>Food Research Institute</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="P117" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
@@ -11142,6 +11314,7 @@
       <c r="AO117" t="inlineStr"/>
       <c r="AP117" t="inlineStr"/>
       <c r="AQ117" t="inlineStr"/>
+      <c r="AR117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -11198,12 +11371,12 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
         <is>
           <t>Mcgill University</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
@@ -11232,6 +11405,7 @@
       <c r="AO118" t="inlineStr"/>
       <c r="AP118" t="inlineStr"/>
       <c r="AQ118" t="inlineStr"/>
+      <c r="AR118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -11290,12 +11464,12 @@
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
         <is>
           <t>Virginia Polytechnic Institute</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
@@ -11324,6 +11498,7 @@
       <c r="AO119" t="inlineStr"/>
       <c r="AP119" t="inlineStr"/>
       <c r="AQ119" t="inlineStr"/>
+      <c r="AR119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -11409,48 +11584,52 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
           <t>* University Of Wisconsin. This Is A Portion Of A Larger Study Dealing With The Relationships Among Education, Ability, And Income, Supported By The Ford Foundation. We Wish To Acknowledge The Financial Support Provided By The Ford Foundation And The Institute For Research On Poverty, University Of Wisconsin. The Basic Data Were Generously Made Available To Us By The U.S. Department Of Labor, Office Of Manpower, Automation And Training. We Are Grateful To A Number Of People For Their Comments, Particularly Arthur S. Goldberger, Samuel Bowles, And Thomas Ribich.  1! For Some Evidence Of The Relatively Low Effectiveness Of Such Programs In Terms Of Monetary Benefits Relative To Costs, See B. A. Weisbrod (1965, Pp. 117-49) And T. Ribich.</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="P120" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr">
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="V120" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
-      <c r="Z120" t="inlineStr">
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="AA120" t="inlineStr">
+      <c r="AB120" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr"/>
       <c r="AD120" t="inlineStr"/>
       <c r="AE120" t="inlineStr"/>
@@ -11466,6 +11645,7 @@
       <c r="AO120" t="inlineStr"/>
       <c r="AP120" t="inlineStr"/>
       <c r="AQ120" t="inlineStr"/>
+      <c r="AR120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -11550,17 +11730,17 @@
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
         <is>
           <t>Florida State University</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="P121" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
@@ -11588,6 +11768,7 @@
       <c r="AO121" t="inlineStr"/>
       <c r="AP121" t="inlineStr"/>
       <c r="AQ121" t="inlineStr"/>
+      <c r="AR121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -11677,50 +11858,54 @@
 ? Computed By The Department Of Commerce.</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
         <is>
           <t>UCB</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="P122" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="Q122" t="inlineStr">
         <is>
           <t>Us Department Of Commerce</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
+      <c r="R122" t="inlineStr">
         <is>
           <t>University Of Wisconsin-Madison</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr">
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
         <is>
           <t>UCB</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="V122" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
+      <c r="W122" t="inlineStr">
         <is>
           <t>Us Department Of Commerce</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>University Of Wisconsin-Madison</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
@@ -11740,6 +11925,7 @@
       <c r="AO122" t="inlineStr"/>
       <c r="AP122" t="inlineStr"/>
       <c r="AQ122" t="inlineStr"/>
+      <c r="AR122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -11798,17 +11984,17 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr">
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
         <is>
           <t>City University Of New York</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="P123" t="inlineStr">
         <is>
           <t>National Bureau Of Economic Research</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr"/>
@@ -11836,6 +12022,7 @@
       <c r="AO123" t="inlineStr"/>
       <c r="AP123" t="inlineStr"/>
       <c r="AQ123" t="inlineStr"/>
+      <c r="AR123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -11905,23 +12092,27 @@
 Helped Enormously In The Development Of Its Ideas.</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr">
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr">
         <is>
           <t>Princeton University</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr"/>
@@ -11944,6 +12135,7 @@
       <c r="AO124" t="inlineStr"/>
       <c r="AP124" t="inlineStr"/>
       <c r="AQ124" t="inlineStr"/>
+      <c r="AR124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -12012,12 +12204,12 @@
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr">
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
         <is>
           <t>UCB</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
@@ -12046,6 +12238,7 @@
       <c r="AO125" t="inlineStr"/>
       <c r="AP125" t="inlineStr"/>
       <c r="AQ125" t="inlineStr"/>
+      <c r="AR125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -12112,12 +12305,12 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr">
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
         <is>
           <t>UCB</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
@@ -12146,6 +12339,7 @@
       <c r="AO126" t="inlineStr"/>
       <c r="AP126" t="inlineStr"/>
       <c r="AQ126" t="inlineStr"/>
+      <c r="AR126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -12212,22 +12406,22 @@
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr">
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
         <is>
           <t>Hebrew University</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="P127" t="inlineStr">
         <is>
           <t>Hebrew University Of Jerusalem</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="Q127" t="inlineStr">
         <is>
           <t>UCB</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
@@ -12254,6 +12448,7 @@
       <c r="AO127" t="inlineStr"/>
       <c r="AP127" t="inlineStr"/>
       <c r="AQ127" t="inlineStr"/>
+      <c r="AR127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -12330,12 +12525,12 @@
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr">
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
         <is>
           <t>UCSB</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
@@ -12364,6 +12559,7 @@
       <c r="AO128" t="inlineStr"/>
       <c r="AP128" t="inlineStr"/>
       <c r="AQ128" t="inlineStr"/>
+      <c r="AR128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -12471,23 +12667,27 @@
 Second-Best Allocation. But These Considerations Do Not</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Author Surname</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
         <is>
           <t>Rand Corporation</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr">
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr">
         <is>
           <t>Rand Corporation</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
@@ -12510,6 +12710,7 @@
       <c r="AO129" t="inlineStr"/>
       <c r="AP129" t="inlineStr"/>
       <c r="AQ129" t="inlineStr"/>
+      <c r="AR129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -12584,12 +12785,12 @@
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
@@ -12618,6 +12819,7 @@
       <c r="AO130" t="inlineStr"/>
       <c r="AP130" t="inlineStr"/>
       <c r="AQ130" t="inlineStr"/>
+      <c r="AR130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -12693,32 +12895,36 @@
 Peared In Modigliani'S 1966 Article.</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
         <is>
           <t>University Of Illinois</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr">
+      <c r="P131" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr">
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
         <is>
           <t>University Of Illinois</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="V131" t="inlineStr">
         <is>
           <t>University Of Wisconsin</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
@@ -12740,6 +12946,7 @@
       <c r="AO131" t="inlineStr"/>
       <c r="AP131" t="inlineStr"/>
       <c r="AQ131" t="inlineStr"/>
+      <c r="AR131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -12830,17 +13037,17 @@
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
+      <c r="P132" t="inlineStr">
         <is>
           <t>U. S. Department Of Labor</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
@@ -12868,6 +13075,7 @@
       <c r="AO132" t="inlineStr"/>
       <c r="AP132" t="inlineStr"/>
       <c r="AQ132" t="inlineStr"/>
+      <c r="AR132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -12936,12 +13144,12 @@
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
         <is>
           <t>University Of Kansas</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
@@ -12970,6 +13178,7 @@
       <c r="AO133" t="inlineStr"/>
       <c r="AP133" t="inlineStr"/>
       <c r="AQ133" t="inlineStr"/>
+      <c r="AR133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -13041,29 +13250,33 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
+          <t>Respectively</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
           <t>*'The Authors Are, Respectively, Professor Of Economics At Harvard University</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
+      <c r="O134" t="inlineStr">
         <is>
           <t>Harvard University</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr">
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr">
         <is>
           <t xml:space="preserve"> And Assistant Professor Of Engineering-Economic Systems And, By Courtesy, Of Economics At Stanford University. R. C. Lind'S Work Has Been Supported By National Science Foundation Grant Nsf-Gk-1683.  1]. Hirshleifer (1965, 1966) And Hirshleifer, J. C. De Haven, And J. W. Milliman (Pp. 139-50).</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="U134" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
@@ -13086,6 +13299,7 @@
       <c r="AO134" t="inlineStr"/>
       <c r="AP134" t="inlineStr"/>
       <c r="AQ134" t="inlineStr"/>
+      <c r="AR134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -13161,23 +13375,27 @@
 Eugene Seskin For Help With Computations.</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
         <is>
           <t>Carnegie-Mellon University</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr">
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
         <is>
           <t>Carnegie-Mellon University</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
@@ -13200,6 +13418,7 @@
       <c r="AO135" t="inlineStr"/>
       <c r="AP135" t="inlineStr"/>
       <c r="AQ135" t="inlineStr"/>
+      <c r="AR135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -13296,12 +13515,12 @@
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
         <is>
           <t>University Of Illinois</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
@@ -13330,6 +13549,7 @@
       <c r="AO136" t="inlineStr"/>
       <c r="AP136" t="inlineStr"/>
       <c r="AQ136" t="inlineStr"/>
+      <c r="AR136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -13384,7 +13604,11 @@
           <t>[ ' T H I S   C O N T E N T   D O W N L O A D E D   F R O M   1 3 7 . 1 5 8 . 1 5 8 . 6 2   O N   W E D ,   1 9   J A N   2 0 2 2   0 9 : 5 1 : 3 9   U T C \ N A I I   U S E   S U B J E C T   T O   H T T P S : / / A B O U T . J S T O R . O R G / T E R M S \ N ' ,   ' 2 5 8 \ N ' ,   ' ' ,   ' Á À   —   A   —   A D 4 \ N ' ,   ' A N D \ N ' ,   ' A 4   —   A / ( A   T   K ) , \ N ' ,   ' ' ,   ' T H E   E R R O R   W A S   P O I N T E D   O U T   B Y   R O B E R T   J . \ N M O R E L A N D   O F   T H E   G O V E R N M E N T   O F   T H E   P R O V - \ N I N C E   O F   N E W   B R U N S W I C K ,   T R E A S U R Y   B O A R D , \ N F R E D E R I C T O N ,   N .   B . ,   A N D   B Y   J .   K .   S T E P H E N S \ N A N D   T .   G .   M A L L I A R I S ,   U N I V E R S I T Y   O F   O K L A H O M A . \ N ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' A M \ N ' ,   ' ' ,   ' 1 C E   C \ N ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   " T   O F   T H \ N ' E A S U R Y \ N " ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' W H E R E \ N ' ,   ' 9 C P / 0 ( M / P )   —   ( 1   —   S ) ( U   T   N . " \ N ' ,   ' R   — I   —   ( A / A   —   F ) W A \ N ' ,   ' ( 3 ) \ N ' ,   " * ' T H U S   T H E   R E A L   B A L A N C E   E F F E C T   I M P L I C I T \ N I N   ( 8 )   I S \ N " ,   ' ' ,   " 1 .   T H E R E   A R E   E R R O R S   I N   T H E   N O T A T I O N   O F   L E S T E R \ N T E L S E R ' S   D I S C U S S I O N   O N   P A G E   1 2 3   O F   T H E \ N M A Y   1 9 6 9   P A P E R S   A N D   P R O C E E D I N G S   I S S U E . \ N T H E   T H R E E   L I N E S   S T A R T I N G   W I T H   E Q U A T I O N   ( 3 ) \ N S H O U L D   R E A D \ N " ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' J \ N ' ,   ' ' ,   ' ' ,   ' J O N   O N   P A G E \ N ' ,   ' ' ,   ' D .   L E V H A R I   A N D   D O N   P A T I N K I N ,   " T H E   R O L E \ N O F   M O N E Y   I N   A   S I M P L E   G R O W T H   M O D E L , " \ N T H I S   R E V I E W ,   S E P T .   1 9 6 8 ,   5 8 ,   P .   7 2 0 ,   L I N E S   1 1 \ N A N D   1 2   S H O U L D   R E A D \ N ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' ' ,   ' 1 \ N ' ,   ' ' ,   ' ' ,   ' E R R A T A \ N ' ,   ' ' ,   ' ' ]</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No split</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
@@ -13415,6 +13639,7 @@
       <c r="AO137" t="inlineStr"/>
       <c r="AP137" t="inlineStr"/>
       <c r="AQ137" t="inlineStr"/>
+      <c r="AR137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
